--- a/workspaces/cobranza/estadisticas/PLANTILLA_ESTADISTICA_JUNTA_MENSUAL_2026_ENERO_VFINAL.xlsx
+++ b/workspaces/cobranza/estadisticas/PLANTILLA_ESTADISTICA_JUNTA_MENSUAL_2026_ENERO_VFINAL.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESTADISTICA 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUÍA KPIs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESTADISTICA 2026" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'ESTADISTICA 2026'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'ESTADISTICA 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="69">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -343,6 +344,88 @@
       <color rgb="00FFD966"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E5FA3"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="002E5FA3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E5FA3"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FF8C00"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="22">
     <fill>
@@ -452,7 +535,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="58">
     <border>
       <left/>
       <right/>
@@ -808,11 +891,319 @@
         <color rgb="00375623"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002E5FA3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002E5FA3"/>
+      </right>
+      <top style="medium">
+        <color rgb="002E5FA3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002E5FA3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002E5FA3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002E5FA3"/>
+      </right>
+      <top style="medium">
+        <color rgb="002E5FA3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002E5FA3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00C00000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00C00000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C00000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00C00000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C00000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00C00000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C00000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C00000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00375623"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00375623"/>
+      </right>
+      <top style="medium">
+        <color rgb="00375623"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00375623"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00375623"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00375623"/>
+      </right>
+      <top style="medium">
+        <color rgb="00375623"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00375623"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00FF8C00"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FF8C00"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FF8C00"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00FF8C00"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FF8C00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FF8C00"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FF8C00"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FF8C00"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1271,6 +1662,210 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="13" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="8" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1670,7 +2265,7 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="204" t="inlineStr">
         <is>
           <t>AÑO 2026</t>
         </is>
@@ -1703,6 +2298,7 @@
           <t>ENERO 2026</t>
         </is>
       </c>
+      <c r="D5" s="162" t="n"/>
       <c r="E5" s="90" t="inlineStr">
         <is>
           <t>AÑO:</t>
@@ -1713,161 +2309,254 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="H5" s="162" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="92" t="inlineStr">
+      <c r="A7" s="217" t="inlineStr">
+        <is>
+          <t>COBRANZA TOTAL
+GENERAL</t>
+        </is>
+      </c>
+      <c r="B7" s="45" t="n"/>
+      <c r="C7" s="46" t="n"/>
+      <c r="D7" s="218" t="inlineStr">
+        <is>
+          <t>COBRANZA
+RECUPERADA</t>
+        </is>
+      </c>
+      <c r="E7" s="45" t="n"/>
+      <c r="F7" s="46" t="n"/>
+      <c r="G7" s="219" t="inlineStr">
+        <is>
+          <t>COBRANZA
+EFECTIVA</t>
+        </is>
+      </c>
+      <c r="H7" s="45" t="n"/>
+      <c r="I7" s="46" t="n"/>
+      <c r="J7" s="220" t="inlineStr">
+        <is>
+          <t>CANCELACIONES</t>
+        </is>
+      </c>
+      <c r="K7" s="45" t="n"/>
+      <c r="L7" s="46" t="n"/>
+      <c r="M7" s="38" t="n"/>
+      <c r="N7" s="38" t="n"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="221" t="inlineStr">
+        <is>
+          <t>$1,408,644</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="n"/>
+      <c r="C8" s="46" t="n"/>
+      <c r="D8" s="222" t="inlineStr">
+        <is>
+          <t>$115,277</t>
+        </is>
+      </c>
+      <c r="E8" s="45" t="n"/>
+      <c r="F8" s="46" t="n"/>
+      <c r="G8" s="223" t="inlineStr">
+        <is>
+          <t>$1,073,301</t>
+        </is>
+      </c>
+      <c r="H8" s="45" t="n"/>
+      <c r="I8" s="46" t="n"/>
+      <c r="J8" s="224" t="inlineStr">
+        <is>
+          <t>$127,110</t>
+        </is>
+      </c>
+      <c r="K8" s="45" t="n"/>
+      <c r="L8" s="46" t="n"/>
+      <c r="M8" s="38" t="n"/>
+      <c r="N8" s="38" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="225" t="inlineStr">
+        <is>
+          <t>88.0% del total</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="n"/>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="226" t="inlineStr">
+        <is>
+          <t>8.2% del total</t>
+        </is>
+      </c>
+      <c r="E9" s="45" t="n"/>
+      <c r="F9" s="46" t="n"/>
+      <c r="G9" s="227" t="inlineStr">
+        <is>
+          <t>76.2% del total</t>
+        </is>
+      </c>
+      <c r="H9" s="45" t="n"/>
+      <c r="I9" s="46" t="n"/>
+      <c r="J9" s="228" t="inlineStr">
+        <is>
+          <t>9.0% del total</t>
+        </is>
+      </c>
+      <c r="K9" s="45" t="n"/>
+      <c r="L9" s="46" t="n"/>
+      <c r="M9" s="38" t="n"/>
+      <c r="N9" s="38" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="n"/>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="38" t="n"/>
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="38" t="n"/>
+      <c r="M10" s="38" t="n"/>
+      <c r="N10" s="38" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="217" t="inlineStr">
         <is>
           <t>COBRANZA
 CORRIENTE</t>
         </is>
       </c>
-      <c r="D7" s="93" t="inlineStr">
-        <is>
-          <t>CANCELACIONES</t>
-        </is>
-      </c>
-      <c r="G7" s="94" t="inlineStr">
+      <c r="B11" s="45" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="229" t="inlineStr">
         <is>
           <t>COBRANZA
 VENCIDA</t>
         </is>
       </c>
-      <c r="J7" s="95" t="inlineStr">
-        <is>
-          <t>COBRANZA
-EFECTIVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="96" t="inlineStr">
-        <is>
-          <t>$1,608,391</t>
-        </is>
-      </c>
-      <c r="D8" s="97" t="inlineStr">
-        <is>
-          <t>$127,110</t>
-        </is>
-      </c>
-      <c r="G8" s="98" t="inlineStr">
-        <is>
-          <t>$166,220</t>
-        </is>
-      </c>
-      <c r="J8" s="99" t="inlineStr">
-        <is>
-          <t>$1,228,968</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="100" t="inlineStr">
-        <is>
-          <t>Total del mes</t>
-        </is>
-      </c>
-      <c r="D9" s="101" t="inlineStr">
-        <is>
-          <t>7.9% del total</t>
-        </is>
-      </c>
-      <c r="G9" s="102" t="inlineStr">
-        <is>
-          <t>10.4% del total</t>
-        </is>
-      </c>
-      <c r="J9" s="103" t="inlineStr">
-        <is>
-          <t>76.7% del total</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="104" t="inlineStr">
-        <is>
-          <t>COBRANZA
-RECUPERADA</t>
-        </is>
-      </c>
-      <c r="D11" s="92" t="inlineStr">
-        <is>
-          <t>COBRANZA TOTAL
-GENERAL</t>
-        </is>
-      </c>
-      <c r="G11" s="105" t="inlineStr">
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="46" t="n"/>
+      <c r="G11" s="230" t="inlineStr">
         <is>
           <t>COBRANZA
 ANTICIPADA</t>
         </is>
       </c>
-      <c r="J11" s="106" t="inlineStr">
-        <is>
-          <t>PROYECCIÓN
+      <c r="H11" s="45" t="n"/>
+      <c r="I11" s="46" t="n"/>
+      <c r="J11" s="231" t="inlineStr">
+        <is>
+          <t>PROYECCION
 SIG. MES</t>
         </is>
       </c>
+      <c r="K11" s="45" t="n"/>
+      <c r="L11" s="46" t="n"/>
+      <c r="M11" s="38" t="n"/>
+      <c r="N11" s="38" t="n"/>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="107" t="inlineStr">
-        <is>
-          <t>$115,277</t>
-        </is>
-      </c>
-      <c r="D12" s="96" t="inlineStr">
-        <is>
-          <t>$1,408,644</t>
-        </is>
-      </c>
-      <c r="G12" s="108" t="inlineStr">
+      <c r="A12" s="221" t="inlineStr">
+        <is>
+          <t>$1,476,747</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="n"/>
+      <c r="C12" s="46" t="n"/>
+      <c r="D12" s="232" t="inlineStr">
+        <is>
+          <t>$166,220</t>
+        </is>
+      </c>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="46" t="n"/>
+      <c r="G12" s="233" t="inlineStr">
         <is>
           <t>$80,464</t>
         </is>
       </c>
-      <c r="J12" s="109" t="inlineStr">
+      <c r="H12" s="45" t="n"/>
+      <c r="I12" s="46" t="n"/>
+      <c r="J12" s="234" t="inlineStr">
         <is>
           <t>$1,158,184</t>
         </is>
       </c>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="46" t="n"/>
+      <c r="M12" s="38" t="n"/>
+      <c r="N12" s="38" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="110" t="inlineStr">
-        <is>
-          <t>7.2% del total</t>
-        </is>
-      </c>
-      <c r="D13" s="100" t="inlineStr">
-        <is>
-          <t>Acumulado</t>
-        </is>
-      </c>
-      <c r="G13" s="111" t="inlineStr">
-        <is>
-          <t>5.0% del total</t>
-        </is>
-      </c>
-      <c r="J13" s="112" t="inlineStr">
-        <is>
-          <t>Febrero 2026 →</t>
-        </is>
-      </c>
+      <c r="A13" s="225" t="inlineStr">
+        <is>
+          <t>Total del mes</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="n"/>
+      <c r="C13" s="46" t="n"/>
+      <c r="D13" s="235" t="inlineStr">
+        <is>
+          <t>11.8% del total</t>
+        </is>
+      </c>
+      <c r="E13" s="45" t="n"/>
+      <c r="F13" s="46" t="n"/>
+      <c r="G13" s="236" t="inlineStr">
+        <is>
+          <t>5.7% del total</t>
+        </is>
+      </c>
+      <c r="H13" s="45" t="n"/>
+      <c r="I13" s="46" t="n"/>
+      <c r="J13" s="237" t="inlineStr">
+        <is>
+          <t>Proyeccion FEB 2026</t>
+        </is>
+      </c>
+      <c r="K13" s="45" t="n"/>
+      <c r="L13" s="46" t="n"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="n"/>
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n"/>
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="38" t="n"/>
+      <c r="J14" s="38" t="n"/>
+      <c r="K14" s="38" t="n"/>
+      <c r="L14" s="38" t="n"/>
+      <c r="M14" s="38" t="n"/>
+      <c r="N14" s="38" t="n"/>
     </row>
     <row r="15" ht="8" customHeight="1">
-      <c r="A15" s="89" t="n"/>
-      <c r="B15" s="89" t="n"/>
-      <c r="C15" s="89" t="n"/>
-      <c r="D15" s="89" t="n"/>
-      <c r="E15" s="89" t="n"/>
-      <c r="F15" s="89" t="n"/>
-      <c r="G15" s="89" t="n"/>
-      <c r="H15" s="89" t="n"/>
-      <c r="I15" s="89" t="n"/>
-      <c r="J15" s="89" t="n"/>
-      <c r="K15" s="89" t="n"/>
-      <c r="L15" s="89" t="n"/>
-      <c r="M15" s="89" t="n"/>
-      <c r="N15" s="89" t="n"/>
+      <c r="A15" s="238" t="n"/>
+      <c r="B15" s="238" t="n"/>
+      <c r="C15" s="238" t="n"/>
+      <c r="D15" s="238" t="n"/>
+      <c r="E15" s="238" t="n"/>
+      <c r="F15" s="238" t="n"/>
+      <c r="G15" s="238" t="n"/>
+      <c r="H15" s="238" t="n"/>
+      <c r="I15" s="238" t="n"/>
+      <c r="J15" s="238" t="n"/>
+      <c r="K15" s="238" t="n"/>
+      <c r="L15" s="238" t="n"/>
+      <c r="M15" s="238" t="n"/>
+      <c r="N15" s="238" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="113" t="inlineStr">
@@ -1900,149 +2589,209 @@
           <t>TOTAL ($)</t>
         </is>
       </c>
+      <c r="C17" s="38" t="n"/>
       <c r="D17" s="116" t="inlineStr">
         <is>
           <t>% PARTICIP.</t>
         </is>
       </c>
+      <c r="E17" s="38" t="n"/>
       <c r="F17" s="116" t="inlineStr">
         <is>
           <t>ESTATUS</t>
         </is>
       </c>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="38" t="n"/>
+      <c r="K17" s="38" t="n"/>
+      <c r="L17" s="38" t="n"/>
+      <c r="M17" s="38" t="n"/>
+      <c r="N17" s="38" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="117" t="inlineStr">
+      <c r="A18" s="176" t="inlineStr">
+        <is>
+          <t>COBRANZA TOTAL GENERAL</t>
+        </is>
+      </c>
+      <c r="B18" s="177" t="n">
+        <v>1408644</v>
+      </c>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="178" t="inlineStr">
+        <is>
+          <t>88.0%</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="179" t="inlineStr">
+        <is>
+          <t>Base del periodo</t>
+        </is>
+      </c>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="38" t="n"/>
+      <c r="I18" s="38" t="n"/>
+      <c r="J18" s="38" t="n"/>
+      <c r="K18" s="38" t="n"/>
+      <c r="L18" s="38" t="n"/>
+      <c r="M18" s="38" t="n"/>
+      <c r="N18" s="38" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="180" t="inlineStr">
+        <is>
+          <t>COBRANZA RECUPERADA</t>
+        </is>
+      </c>
+      <c r="B19" s="181" t="n">
+        <v>115277</v>
+      </c>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="182" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="183" t="inlineStr">
+        <is>
+          <t>▲ vs mes anterior</t>
+        </is>
+      </c>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="38" t="n"/>
+      <c r="M19" s="38" t="n"/>
+      <c r="N19" s="38" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="184" t="inlineStr">
         <is>
           <t>COBRANZA EFECTIVA</t>
         </is>
       </c>
-      <c r="B18" s="50" t="n">
-        <v>1228968</v>
-      </c>
-      <c r="D18" s="118" t="inlineStr">
-        <is>
-          <t>76.7%</t>
-        </is>
-      </c>
-      <c r="F18" s="52" t="inlineStr">
-        <is>
-          <t>▲ 8.5% vs mes anterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="119" t="inlineStr">
+      <c r="B20" s="185" t="n">
+        <v>1073301</v>
+      </c>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="186" t="inlineStr">
+        <is>
+          <t>76.2%</t>
+        </is>
+      </c>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="187" t="inlineStr">
+        <is>
+          <t>▲ vs mes anterior</t>
+        </is>
+      </c>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="38" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="38" t="n"/>
+      <c r="K20" s="38" t="n"/>
+      <c r="L20" s="38" t="n"/>
+      <c r="M20" s="38" t="n"/>
+      <c r="N20" s="38" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="188" t="inlineStr">
         <is>
           <t>CANCELACIONES</t>
         </is>
       </c>
-      <c r="B19" s="55" t="n">
+      <c r="B21" s="189" t="n">
         <v>127110</v>
       </c>
-      <c r="D19" s="120" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="F19" s="121" t="inlineStr">
-        <is>
-          <t>▼ 1.1% vs mes anterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="122" t="inlineStr">
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="190" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="191" t="inlineStr">
+        <is>
+          <t>▼ vs mes anterior</t>
+        </is>
+      </c>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="38" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="38" t="n"/>
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="38" t="n"/>
+      <c r="M21" s="38" t="n"/>
+      <c r="N21" s="38" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="192" t="inlineStr">
         <is>
           <t>COBRANZA VENCIDA</t>
         </is>
       </c>
-      <c r="B20" s="59" t="n">
+      <c r="B22" s="193" t="n">
         <v>166220</v>
       </c>
-      <c r="D20" s="123" t="inlineStr">
-        <is>
-          <t>10.4%</t>
-        </is>
-      </c>
-      <c r="F20" s="61" t="inlineStr">
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="194" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="E22" s="38" t="n"/>
+      <c r="F22" s="195" t="inlineStr">
         <is>
           <t>▼ vs mes anterior</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="124" t="inlineStr">
-        <is>
-          <t>COBRANZA ANTICIPADA</t>
-        </is>
-      </c>
-      <c r="B21" s="125" t="n">
-        <v>80464</v>
-      </c>
-      <c r="D21" s="126" t="inlineStr">
-        <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-      <c r="F21" s="127" t="inlineStr">
-        <is>
-          <t>Sin cambios</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="128" t="inlineStr">
-        <is>
-          <t>TOTAL CONCENTRADO</t>
-        </is>
-      </c>
-      <c r="B22" s="129" t="n">
-        <v>1602762</v>
-      </c>
-      <c r="C22" s="130" t="n"/>
-      <c r="D22" s="131" t="inlineStr">
+      <c r="G22" s="38" t="n"/>
+      <c r="H22" s="38" t="n"/>
+      <c r="I22" s="38" t="n"/>
+      <c r="J22" s="38" t="n"/>
+      <c r="K22" s="38" t="n"/>
+      <c r="L22" s="38" t="n"/>
+      <c r="M22" s="38" t="n"/>
+      <c r="N22" s="38" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="196" t="inlineStr">
+        <is>
+          <t>TOTAL ACUMULADO</t>
+        </is>
+      </c>
+      <c r="B23" s="197" t="n">
+        <v>2890552</v>
+      </c>
+      <c r="C23" s="130" t="n"/>
+      <c r="D23" s="198" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E22" s="130" t="n"/>
-      <c r="F22" s="132" t="inlineStr">
-        <is>
-          <t>Desglose del mes</t>
-        </is>
-      </c>
-      <c r="G22" s="130" t="n"/>
-      <c r="H22" s="130" t="n"/>
-      <c r="I22" s="130" t="n"/>
-      <c r="J22" s="130" t="n"/>
-      <c r="K22" s="130" t="n"/>
-      <c r="L22" s="130" t="n"/>
-      <c r="M22" s="130" t="n"/>
-      <c r="N22" s="130" t="n"/>
-    </row>
-    <row r="23" ht="8" customHeight="1">
-      <c r="A23" s="89" t="n"/>
-      <c r="B23" s="89" t="n"/>
-      <c r="C23" s="89" t="n"/>
-      <c r="D23" s="89" t="n"/>
-      <c r="E23" s="89" t="n"/>
-      <c r="F23" s="89" t="n"/>
-      <c r="G23" s="89" t="n"/>
-      <c r="H23" s="89" t="n"/>
-      <c r="I23" s="89" t="n"/>
-      <c r="J23" s="89" t="n"/>
-      <c r="K23" s="89" t="n"/>
-      <c r="L23" s="89" t="n"/>
-      <c r="M23" s="89" t="n"/>
-      <c r="N23" s="89" t="n"/>
+      <c r="E23" s="130" t="n"/>
+      <c r="F23" s="199" t="inlineStr">
+        <is>
+          <t>Suma de todos los conceptos</t>
+        </is>
+      </c>
+      <c r="G23" s="130" t="n"/>
+      <c r="H23" s="130" t="n"/>
+      <c r="I23" s="130" t="n"/>
+      <c r="J23" s="130" t="n"/>
+      <c r="K23" s="130" t="n"/>
+      <c r="L23" s="130" t="n"/>
+      <c r="M23" s="130" t="n"/>
+      <c r="N23" s="130" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="113" t="inlineStr">
-        <is>
-          <t>TOP 5 POR CATEGORÍA — ENERO 2026</t>
-        </is>
-      </c>
+      <c r="A24" s="239" t="n"/>
       <c r="B24" s="114" t="n"/>
       <c r="C24" s="114" t="n"/>
       <c r="D24" s="114" t="n"/>
@@ -2501,7 +3250,7 @@
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="159" t="inlineStr">
+      <c r="A43" s="216" t="inlineStr">
         <is>
           <t>PROTEG-RT MUTUALIDAD  |  Gerencia de Cobranza  |  Reporte Mensual — Luna Dashboard</t>
         </is>
@@ -2558,6 +3307,326 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="202" t="inlineStr">
+        <is>
+          <t>PROTEG-RT MUTUALIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="203" t="inlineStr">
+        <is>
+          <t>GUÍA DE KPIs — DICCIONARIO DE MÉTRICAS DE COBRANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="204" t="inlineStr">
+        <is>
+          <t>AÑO 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="89" t="n"/>
+      <c r="B4" s="89" t="n"/>
+      <c r="C4" s="89" t="n"/>
+      <c r="D4" s="89" t="n"/>
+      <c r="E4" s="89" t="n"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="205" t="inlineStr">
+        <is>
+          <t>Este documento describe cada KPI del Dashboard y Plantilla de Estadísticas. Sirve como guía para interpretar los datos y entender cómo se calcula cada métrica. Cada KPI corresponde a una sección del reporte mensual de cobranza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="206" t="inlineStr">
+        <is>
+          <t>MÉTRICA</t>
+        </is>
+      </c>
+      <c r="B7" s="206" t="inlineStr">
+        <is>
+          <t>TOTAL ($) — ENE 2026</t>
+        </is>
+      </c>
+      <c r="C7" s="206" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="D7" s="206" t="inlineStr">
+        <is>
+          <t>¿CÓMO SE INTERPRETA?</t>
+        </is>
+      </c>
+      <c r="E7" s="206" t="inlineStr">
+        <is>
+          <t>FÓRMULA / FUENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="207" t="inlineStr">
+        <is>
+          <t>COBRANZA TOTAL GENERAL</t>
+        </is>
+      </c>
+      <c r="B8" s="208" t="inlineStr">
+        <is>
+          <t>$1,408,644</t>
+        </is>
+      </c>
+      <c r="C8" s="209" t="inlineStr">
+        <is>
+          <t>Es el monto total de toda la facturación emitida en el mes. Incluye todos los contratos nuevos y renovaciones generados en el periodo.</t>
+        </is>
+      </c>
+      <c r="D8" s="209" t="inlineStr">
+        <is>
+          <t>Representa el universo completo de facturación. Es el punto de partida para calcular todos los demás porcentajes de eficiencia.</t>
+        </is>
+      </c>
+      <c r="E8" s="210">
+        <f> Suma de TOTAL GENERAL (columna Z/AA del reporte). Se toma sin filtro de STATUS.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="211" t="inlineStr">
+        <is>
+          <t>COBRANZA RECUPERADA</t>
+        </is>
+      </c>
+      <c r="B9" s="212" t="inlineStr">
+        <is>
+          <t>$115,277</t>
+        </is>
+      </c>
+      <c r="C9" s="213" t="inlineStr">
+        <is>
+          <t>Son las cuentas que estavam vencidas (atrasadas de meses anteriores) y que en este mes lograron recuperase mediante pago.</t>
+        </is>
+      </c>
+      <c r="D9" s="213" t="inlineStr">
+        <is>
+          <t>Un valor alto indica que se está haciendo buen trabajo de cobranza sobre cartera vieja. Meta: maximizar este indicador.</t>
+        </is>
+      </c>
+      <c r="E9" s="214">
+        <f> Suma de MONTO (columna AV) en apartado RECUPERADA, sin filtro STATUS. Top 5 agrupa por COBRADO (columna BA).</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="207" t="inlineStr">
+        <is>
+          <t>COBRANZA EFECTIVA</t>
+        </is>
+      </c>
+      <c r="B10" s="208" t="inlineStr">
+        <is>
+          <t>$1,228,968</t>
+        </is>
+      </c>
+      <c r="C10" s="209" t="inlineStr">
+        <is>
+          <t>Es el monto cobrado durante el mes que corresponde a ventas del MISMO periodo de facturación (no incluye cartera vencida).</t>
+        </is>
+      </c>
+      <c r="D10" s="209" t="inlineStr">
+        <is>
+          <t>Es el indicador principal de eficiencia de cobranza. Compara cuánto se cobró vs cuánto se emitió. Meta: &gt;75%.</t>
+        </is>
+      </c>
+      <c r="E10" s="210">
+        <f> Suma de MONTO (columna AK) en apartado EFECTIVA, sin filtro STATUS. Top 5 agrupa por COBRADO (columna AP).</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="211" t="inlineStr">
+        <is>
+          <t>CANCELACIONES</t>
+        </is>
+      </c>
+      <c r="B11" s="212" t="inlineStr">
+        <is>
+          <t>$127,110</t>
+        </is>
+      </c>
+      <c r="C11" s="213" t="inlineStr">
+        <is>
+          <t>Son las pólizas que fueron canceladas durante el mes, ya sea por falta de pago o por decisión del cliente.</t>
+        </is>
+      </c>
+      <c r="D11" s="213" t="inlineStr">
+        <is>
+          <t>Un valor alto puede indicar problemas en la calidad de la venta o en la gestión de cobranza preventiva. Revisar causa raíz.</t>
+        </is>
+      </c>
+      <c r="E11" s="214">
+        <f> Suma de MONTO en apartado CANCELACIONES, sin filtro STATUS. Top 5 agrupa por VENDEDOR (columna U/V).</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="207" t="inlineStr">
+        <is>
+          <t>COBRANZA VENCIDA</t>
+        </is>
+      </c>
+      <c r="B12" s="208" t="inlineStr">
+        <is>
+          <t>$166,220</t>
+        </is>
+      </c>
+      <c r="C12" s="209" t="inlineStr">
+        <is>
+          <t>Son las cuentas que tenían atraso y NO se recuperaron en el mes. Representa la cartera vencida pendiente de cobro.</t>
+        </is>
+      </c>
+      <c r="D12" s="209" t="inlineStr">
+        <is>
+          <t>Un valor bajo es bueno (significa que se está recuperando la cartera vencida). Un valor alto requiere acción inmediata.</t>
+        </is>
+      </c>
+      <c r="E12" s="210">
+        <f> Suma de MONTO en apartado VENCIDA/ATRASADA, sin filtro STATUS. Top 5 agrupa por UBICACIÓN_T (columna V).</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="211" t="inlineStr">
+        <is>
+          <t>COBRANZA CORRIENTE</t>
+        </is>
+      </c>
+      <c r="B13" s="212" t="inlineStr">
+        <is>
+          <t>$1,608,391</t>
+        </is>
+      </c>
+      <c r="C13" s="213" t="inlineStr">
+        <is>
+          <t>Es el monto total de la cartera ACTUAL (vence en el mes actual). Es la base de la operación normal de cobranza.</t>
+        </is>
+      </c>
+      <c r="D13" s="213" t="inlineStr">
+        <is>
+          <t>Es la referencia principal para evaluar el desempeño del equipo. Representa la facturación reciente pendiente de cobro.</t>
+        </is>
+      </c>
+      <c r="E13" s="214">
+        <f> Suma de MONTO (columna Z) en apartado CORRIENTE, sin filtro STATUS. Top 5 agrupa por VENDEDOR (columna U).</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="207" t="inlineStr">
+        <is>
+          <t>COBRANZA ANTICIPADA</t>
+        </is>
+      </c>
+      <c r="B14" s="208" t="inlineStr">
+        <is>
+          <t>$80,464</t>
+        </is>
+      </c>
+      <c r="C14" s="209" t="inlineStr">
+        <is>
+          <t>Son pagos que el cliente realizó ANTES de la fecha de vencimiento. Indica buen comportamiento de pago.</t>
+        </is>
+      </c>
+      <c r="D14" s="209" t="inlineStr">
+        <is>
+          <t>Un valor positivo es favorable: significa que hay clientes que pagan antes de tiempo, lo cual mejora el flujo de caja.</t>
+        </is>
+      </c>
+      <c r="E14" s="210">
+        <f> Suma de MONTO (columna BG) en apartado ADELANTADA FUTURA, sin filtro STATUS. Top 5 agrupa por COBRADO (columna BL).</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="211" t="inlineStr">
+        <is>
+          <t>PROYECCIÓN (SIG. MES)</t>
+        </is>
+      </c>
+      <c r="B15" s="212" t="inlineStr">
+        <is>
+          <t>$1,158,184</t>
+        </is>
+      </c>
+      <c r="C15" s="213" t="inlineStr">
+        <is>
+          <t>Es la estimación de cuánto se cobrará en el MES SIGUIENTE basándose en la tendencia actual de cobranza efectiva.</t>
+        </is>
+      </c>
+      <c r="D15" s="213" t="inlineStr">
+        <is>
+          <t>Se usa para planeación financiera y de operación. No es un compromiso de cobro, sino una referencia proyectada.</t>
+        </is>
+      </c>
+      <c r="E15" s="214">
+        <f> Calculado por el sistema con base en el promedio de cobranza efectiva de los últimos 3 meses.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="8" customHeight="1">
+      <c r="A17" s="89" t="n"/>
+      <c r="B17" s="89" t="n"/>
+      <c r="C17" s="89" t="n"/>
+      <c r="D17" s="89" t="n"/>
+      <c r="E17" s="89" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="215" t="inlineStr">
+        <is>
+          <t>📌 Nota: Los valores en la columna 'TOTAL ($) — ENE 2026' son ejemplos del mes de referencia (Enero 2026). Al cargar datos de otros meses, los totales se actualizan automáticamente en la Plantilla Principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="216" t="inlineStr">
+        <is>
+          <t>PROTEG-RT MUTUALIDAD  |  Gerencia de Cobranza  |  Guía de KPIs — Luna Dashboard</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O914"/>
@@ -2836,24 +3905,24 @@
       <c r="N14" s="48" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
-        <is>
-          <t>COBRANZA EFECTIVA</t>
-        </is>
-      </c>
-      <c r="B15" s="50" t="n">
-        <v>1228968</v>
+      <c r="A15" s="176" t="inlineStr">
+        <is>
+          <t>COBRANZA TOTAL GENERAL</t>
+        </is>
+      </c>
+      <c r="B15" s="177" t="n">
+        <v>1408644</v>
       </c>
       <c r="C15" s="48" t="n"/>
-      <c r="D15" s="51" t="inlineStr">
-        <is>
-          <t>76.7%</t>
+      <c r="D15" s="200" t="inlineStr">
+        <is>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="E15" s="48" t="n"/>
-      <c r="F15" s="52" t="inlineStr">
-        <is>
-          <t>▲ 8.5% vs mes ant.</t>
+      <c r="F15" s="179" t="inlineStr">
+        <is>
+          <t>Acumulado del mes</t>
         </is>
       </c>
       <c r="G15" s="48" t="n"/>
@@ -2866,24 +3935,24 @@
       <c r="N15" s="53" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="54" t="inlineStr">
-        <is>
-          <t>CANCELACIONES</t>
-        </is>
-      </c>
-      <c r="B16" s="55" t="n">
-        <v>127110</v>
+      <c r="A16" s="180" t="inlineStr">
+        <is>
+          <t>COBRANZA RECUPERADA</t>
+        </is>
+      </c>
+      <c r="B16" s="181" t="n">
+        <v>115277</v>
       </c>
       <c r="C16" s="48" t="n"/>
-      <c r="D16" s="56" t="inlineStr">
-        <is>
-          <t>7.9%</t>
+      <c r="D16" s="182" t="inlineStr">
+        <is>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="E16" s="48" t="n"/>
-      <c r="F16" s="57" t="inlineStr">
-        <is>
-          <t>▼ 1.1% vs mes ant.</t>
+      <c r="F16" s="201" t="inlineStr">
+        <is>
+          <t>▲ 2.3% vs mes anterior</t>
         </is>
       </c>
       <c r="G16" s="48" t="n"/>
@@ -2896,24 +3965,24 @@
       <c r="N16" s="53" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="58" t="inlineStr">
-        <is>
-          <t>COBRANZA VENCIDA</t>
-        </is>
-      </c>
-      <c r="B17" s="59" t="n">
-        <v>166220</v>
+      <c r="A17" s="184" t="inlineStr">
+        <is>
+          <t>COBRANZA EFECTIVA</t>
+        </is>
+      </c>
+      <c r="B17" s="185" t="n">
+        <v>1228968</v>
       </c>
       <c r="C17" s="48" t="n"/>
-      <c r="D17" s="60" t="inlineStr">
-        <is>
-          <t>10.4%</t>
+      <c r="D17" s="186" t="inlineStr">
+        <is>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="E17" s="48" t="n"/>
-      <c r="F17" s="61" t="inlineStr">
-        <is>
-          <t>▼ vs mes anterior</t>
+      <c r="F17" s="187" t="inlineStr">
+        <is>
+          <t>▲ 8.5% vs mes anterior</t>
         </is>
       </c>
       <c r="G17" s="48" t="n"/>
@@ -2926,24 +3995,24 @@
       <c r="N17" s="53" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>COBRANZA ANTICIPADA</t>
-        </is>
-      </c>
-      <c r="B18" s="63" t="n">
-        <v>80464</v>
+      <c r="A18" s="188" t="inlineStr">
+        <is>
+          <t>CANCELACIONES</t>
+        </is>
+      </c>
+      <c r="B18" s="189" t="n">
+        <v>127110</v>
       </c>
       <c r="C18" s="48" t="n"/>
-      <c r="D18" s="64" t="inlineStr">
-        <is>
-          <t>5.0%</t>
+      <c r="D18" s="190" t="inlineStr">
+        <is>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="E18" s="48" t="n"/>
-      <c r="F18" s="65" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F18" s="191" t="inlineStr">
+        <is>
+          <t>▼ 1.1% vs mes anterior</t>
         </is>
       </c>
       <c r="G18" s="48" t="n"/>
@@ -2955,25 +4024,25 @@
       <c r="M18" s="53" t="n"/>
       <c r="N18" s="53" t="n"/>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="66" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="67" t="n">
-        <v>1602762</v>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="192" t="inlineStr">
+        <is>
+          <t>COBRANZA VENCIDA</t>
+        </is>
+      </c>
+      <c r="B19" s="193" t="n">
+        <v>166220</v>
       </c>
       <c r="C19" s="48" t="n"/>
-      <c r="D19" s="68" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="D19" s="194" t="inlineStr">
+        <is>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="E19" s="48" t="n"/>
-      <c r="F19" s="69" t="inlineStr">
-        <is>
-          <t>Total concentrado del mes</t>
+      <c r="F19" s="195" t="inlineStr">
+        <is>
+          <t>▼ vs mes anterior</t>
         </is>
       </c>
       <c r="G19" s="45" t="n"/>
@@ -2985,21 +4054,35 @@
       <c r="M19" s="53" t="n"/>
       <c r="N19" s="53" t="n"/>
     </row>
-    <row r="20" ht="6" customHeight="1">
-      <c r="A20" s="83" t="n"/>
-      <c r="B20" s="83" t="n"/>
-      <c r="C20" s="83" t="n"/>
-      <c r="D20" s="83" t="n"/>
-      <c r="E20" s="83" t="n"/>
-      <c r="F20" s="83" t="n"/>
-      <c r="G20" s="83" t="n"/>
-      <c r="H20" s="83" t="n"/>
-      <c r="I20" s="83" t="n"/>
-      <c r="J20" s="83" t="n"/>
-      <c r="K20" s="83" t="n"/>
-      <c r="L20" s="83" t="n"/>
-      <c r="M20" s="83" t="n"/>
-      <c r="N20" s="83" t="n"/>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="196" t="inlineStr">
+        <is>
+          <t>TOTAL ACUMULADO</t>
+        </is>
+      </c>
+      <c r="B20" s="197" t="n">
+        <v>3046219</v>
+      </c>
+      <c r="C20" s="130" t="n"/>
+      <c r="D20" s="198" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E20" s="130" t="n"/>
+      <c r="F20" s="199" t="inlineStr">
+        <is>
+          <t>Suma de todos los conceptos</t>
+        </is>
+      </c>
+      <c r="G20" s="130" t="n"/>
+      <c r="H20" s="130" t="n"/>
+      <c r="I20" s="130" t="n"/>
+      <c r="J20" s="130" t="n"/>
+      <c r="K20" s="130" t="n"/>
+      <c r="L20" s="130" t="n"/>
+      <c r="M20" s="130" t="n"/>
+      <c r="N20" s="130" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="84" t="inlineStr">
@@ -4208,7 +5291,7 @@
     <row r="75">
       <c r="A75" s="82" t="inlineStr">
         <is>
-          <t>PROYECCIÓN ENERO → ENERO</t>
+          <t>PROYECCION ENERO  FEBRERO</t>
         </is>
       </c>
       <c r="B75" s="28" t="n"/>
@@ -4228,7 +5311,7 @@
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>Proyección ENERO</t>
+          <t>Proyeccion FEBRERO</t>
         </is>
       </c>
       <c r="B76" s="33" t="n">

--- a/workspaces/cobranza/estadisticas/PLANTILLA_ESTADISTICA_JUNTA_MENSUAL_2026_ENERO_VFINAL.xlsx
+++ b/workspaces/cobranza/estadisticas/PLANTILLA_ESTADISTICA_JUNTA_MENSUAL_2026_ENERO_VFINAL.xlsx
@@ -1203,7 +1203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1865,6 +1865,76 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="8" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2314,8 +2384,8 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="217" t="inlineStr">
         <is>
-          <t>COBRANZA TOTAL
-GENERAL</t>
+          <t>COBRANZA
+TOTAL GENERAL</t>
         </is>
       </c>
       <c r="B7" s="45" t="n"/>
@@ -2349,39 +2419,39 @@
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="221" t="inlineStr">
         <is>
-          <t>$1,408,644</t>
-        </is>
-      </c>
-      <c r="B8" s="45" t="n"/>
-      <c r="C8" s="46" t="n"/>
+          <t>$1,259,266</t>
+        </is>
+      </c>
+      <c r="B8" s="163" t="n"/>
+      <c r="C8" s="164" t="n"/>
       <c r="D8" s="222" t="inlineStr">
         <is>
-          <t>$115,277</t>
-        </is>
-      </c>
-      <c r="E8" s="45" t="n"/>
-      <c r="F8" s="46" t="n"/>
+          <t>$103,509</t>
+        </is>
+      </c>
+      <c r="E8" s="171" t="n"/>
+      <c r="F8" s="172" t="n"/>
       <c r="G8" s="223" t="inlineStr">
         <is>
           <t>$1,073,301</t>
         </is>
       </c>
-      <c r="H8" s="45" t="n"/>
-      <c r="I8" s="46" t="n"/>
+      <c r="H8" s="169" t="n"/>
+      <c r="I8" s="170" t="n"/>
       <c r="J8" s="224" t="inlineStr">
         <is>
           <t>$127,110</t>
         </is>
       </c>
-      <c r="K8" s="45" t="n"/>
-      <c r="L8" s="46" t="n"/>
+      <c r="K8" s="165" t="n"/>
+      <c r="L8" s="166" t="n"/>
       <c r="M8" s="38" t="n"/>
       <c r="N8" s="38" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="225" t="inlineStr">
         <is>
-          <t>88.0% del total</t>
+          <t>85.2% del total</t>
         </is>
       </c>
       <c r="B9" s="45" t="n"/>
@@ -2395,14 +2465,14 @@
       <c r="F9" s="46" t="n"/>
       <c r="G9" s="227" t="inlineStr">
         <is>
-          <t>76.2% del total</t>
+          <t>85.2% del total</t>
         </is>
       </c>
       <c r="H9" s="45" t="n"/>
       <c r="I9" s="46" t="n"/>
       <c r="J9" s="228" t="inlineStr">
         <is>
-          <t>9.0% del total</t>
+          <t>10.1% del total</t>
         </is>
       </c>
       <c r="K9" s="45" t="n"/>
@@ -2468,29 +2538,29 @@
           <t>$1,476,747</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n"/>
-      <c r="C12" s="46" t="n"/>
+      <c r="B12" s="163" t="n"/>
+      <c r="C12" s="164" t="n"/>
       <c r="D12" s="232" t="inlineStr">
         <is>
           <t>$166,220</t>
         </is>
       </c>
-      <c r="E12" s="45" t="n"/>
-      <c r="F12" s="46" t="n"/>
+      <c r="E12" s="167" t="n"/>
+      <c r="F12" s="168" t="n"/>
       <c r="G12" s="233" t="inlineStr">
         <is>
-          <t>$80,464</t>
-        </is>
-      </c>
-      <c r="H12" s="45" t="n"/>
-      <c r="I12" s="46" t="n"/>
+          <t>$4,788</t>
+        </is>
+      </c>
+      <c r="H12" s="173" t="n"/>
+      <c r="I12" s="174" t="n"/>
       <c r="J12" s="234" t="inlineStr">
         <is>
-          <t>$1,158,184</t>
-        </is>
-      </c>
-      <c r="K12" s="45" t="n"/>
-      <c r="L12" s="46" t="n"/>
+          <t>$1,053,199</t>
+        </is>
+      </c>
+      <c r="K12" s="175" t="n"/>
+      <c r="L12" s="162" t="n"/>
       <c r="M12" s="38" t="n"/>
       <c r="N12" s="38" t="n"/>
     </row>
@@ -2504,14 +2574,14 @@
       <c r="C13" s="46" t="n"/>
       <c r="D13" s="235" t="inlineStr">
         <is>
-          <t>11.8% del total</t>
+          <t>13.2% del total</t>
         </is>
       </c>
       <c r="E13" s="45" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="236" t="inlineStr">
         <is>
-          <t>5.7% del total</t>
+          <t>0.4% del total</t>
         </is>
       </c>
       <c r="H13" s="45" t="n"/>
@@ -2617,12 +2687,12 @@
         </is>
       </c>
       <c r="B18" s="177" t="n">
-        <v>1408644</v>
+        <v>1259266</v>
       </c>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="178" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E18" s="38" t="n"/>
@@ -2647,7 +2717,7 @@
         </is>
       </c>
       <c r="B19" s="181" t="n">
-        <v>115277</v>
+        <v>103509</v>
       </c>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="182" t="inlineStr">
@@ -2658,7 +2728,7 @@
       <c r="E19" s="38" t="n"/>
       <c r="F19" s="183" t="inlineStr">
         <is>
-          <t>▲ vs mes anterior</t>
+          <t>Acumulado del mes</t>
         </is>
       </c>
       <c r="G19" s="38" t="n"/>
@@ -2682,13 +2752,13 @@
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="186" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="E20" s="38" t="n"/>
       <c r="F20" s="187" t="inlineStr">
         <is>
-          <t>▲ vs mes anterior</t>
+          <t>Cobrado en el mes</t>
         </is>
       </c>
       <c r="G20" s="38" t="n"/>
@@ -2712,13 +2782,13 @@
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="190" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="E21" s="38" t="n"/>
       <c r="F21" s="191" t="inlineStr">
         <is>
-          <t>▼ vs mes anterior</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G21" s="38" t="n"/>
@@ -2742,13 +2812,13 @@
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="194" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="E22" s="38" t="n"/>
       <c r="F22" s="195" t="inlineStr">
         <is>
-          <t>▼ vs mes anterior</t>
+          <t>En riesgo</t>
         </is>
       </c>
       <c r="G22" s="38" t="n"/>
@@ -2767,7 +2837,7 @@
         </is>
       </c>
       <c r="B23" s="197" t="n">
-        <v>2890552</v>
+        <v>2729406</v>
       </c>
       <c r="C23" s="130" t="n"/>
       <c r="D23" s="198" t="inlineStr">
@@ -2792,19 +2862,19 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="239" t="n"/>
-      <c r="B24" s="114" t="n"/>
-      <c r="C24" s="114" t="n"/>
-      <c r="D24" s="114" t="n"/>
-      <c r="E24" s="114" t="n"/>
-      <c r="F24" s="114" t="n"/>
-      <c r="G24" s="114" t="n"/>
-      <c r="H24" s="114" t="n"/>
-      <c r="I24" s="114" t="n"/>
-      <c r="J24" s="114" t="n"/>
-      <c r="K24" s="114" t="n"/>
-      <c r="L24" s="114" t="n"/>
-      <c r="M24" s="114" t="n"/>
-      <c r="N24" s="115" t="n"/>
+      <c r="B24" s="45" t="n"/>
+      <c r="C24" s="45" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="45" t="n"/>
+      <c r="F24" s="45" t="n"/>
+      <c r="G24" s="45" t="n"/>
+      <c r="H24" s="45" t="n"/>
+      <c r="I24" s="45" t="n"/>
+      <c r="J24" s="45" t="n"/>
+      <c r="K24" s="45" t="n"/>
+      <c r="L24" s="45" t="n"/>
+      <c r="M24" s="45" t="n"/>
+      <c r="N24" s="46" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="133" t="inlineStr">
@@ -3629,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O914"/>
+  <dimension ref="A1:P914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3816,8 +3886,8 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B11" s="41" t="n">
-        <v>1608391</v>
+      <c r="B11" s="260" t="n">
+        <v>1476747</v>
       </c>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="38" t="n"/>
@@ -3853,11 +3923,7 @@
       <c r="N12" s="38" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>📊 CONCENTRADO GENERAL — DISTRIBUCIÓN DEL MES</t>
-        </is>
-      </c>
+      <c r="A13" s="240" t="n"/>
       <c r="B13" s="45" t="n"/>
       <c r="C13" s="45" t="n"/>
       <c r="D13" s="45" t="n"/>
@@ -3865,224 +3931,140 @@
       <c r="F13" s="45" t="n"/>
       <c r="G13" s="45" t="n"/>
       <c r="H13" s="46" t="n"/>
-      <c r="I13" s="38" t="n"/>
-      <c r="J13" s="38" t="n"/>
-      <c r="K13" s="38" t="n"/>
-      <c r="L13" s="38" t="n"/>
-      <c r="M13" s="38" t="n"/>
-      <c r="N13" s="38" t="n"/>
+      <c r="I13" s="83" t="n"/>
+      <c r="J13" s="83" t="n"/>
+      <c r="K13" s="83" t="n"/>
+      <c r="L13" s="83" t="n"/>
+      <c r="M13" s="83" t="n"/>
+      <c r="N13" s="83" t="n"/>
+      <c r="O13" s="70" t="n"/>
+      <c r="P13" s="70" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
-        <is>
-          <t>CONCEPTO</t>
-        </is>
-      </c>
-      <c r="B14" s="47" t="inlineStr">
-        <is>
-          <t>TOTAL ($)</t>
-        </is>
-      </c>
-      <c r="C14" s="48" t="n"/>
-      <c r="D14" s="47" t="inlineStr">
-        <is>
-          <t>% PARTICIP.</t>
-        </is>
-      </c>
-      <c r="E14" s="48" t="n"/>
-      <c r="F14" s="47" t="inlineStr">
-        <is>
-          <t>ESTATUS</t>
-        </is>
-      </c>
-      <c r="G14" s="48" t="n"/>
-      <c r="H14" s="48" t="n"/>
-      <c r="I14" s="48" t="n"/>
-      <c r="J14" s="48" t="n"/>
-      <c r="K14" s="48" t="n"/>
-      <c r="L14" s="48" t="n"/>
-      <c r="M14" s="48" t="n"/>
-      <c r="N14" s="48" t="n"/>
+      <c r="A14" s="241" t="n"/>
+      <c r="B14" s="241" t="n"/>
+      <c r="C14" s="242" t="n"/>
+      <c r="D14" s="241" t="n"/>
+      <c r="E14" s="242" t="n"/>
+      <c r="F14" s="241" t="n"/>
+      <c r="G14" s="242" t="n"/>
+      <c r="H14" s="242" t="n"/>
+      <c r="I14" s="242" t="n"/>
+      <c r="J14" s="242" t="n"/>
+      <c r="K14" s="242" t="n"/>
+      <c r="L14" s="242" t="n"/>
+      <c r="M14" s="242" t="n"/>
+      <c r="N14" s="242" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="70" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="176" t="inlineStr">
-        <is>
-          <t>COBRANZA TOTAL GENERAL</t>
-        </is>
-      </c>
-      <c r="B15" s="177" t="n">
-        <v>1408644</v>
-      </c>
-      <c r="C15" s="48" t="n"/>
-      <c r="D15" s="200" t="inlineStr">
-        <is>
-          <t>88.0%</t>
-        </is>
-      </c>
-      <c r="E15" s="48" t="n"/>
-      <c r="F15" s="179" t="inlineStr">
-        <is>
-          <t>Acumulado del mes</t>
-        </is>
-      </c>
-      <c r="G15" s="48" t="n"/>
-      <c r="H15" s="48" t="n"/>
-      <c r="I15" s="48" t="n"/>
-      <c r="J15" s="48" t="n"/>
-      <c r="K15" s="48" t="n"/>
-      <c r="L15" s="48" t="n"/>
-      <c r="M15" s="53" t="n"/>
-      <c r="N15" s="53" t="n"/>
+      <c r="A15" s="124" t="n"/>
+      <c r="B15" s="125" t="n"/>
+      <c r="C15" s="242" t="n"/>
+      <c r="D15" s="243" t="n"/>
+      <c r="E15" s="242" t="n"/>
+      <c r="F15" s="244" t="n"/>
+      <c r="G15" s="242" t="n"/>
+      <c r="H15" s="242" t="n"/>
+      <c r="I15" s="242" t="n"/>
+      <c r="J15" s="242" t="n"/>
+      <c r="K15" s="242" t="n"/>
+      <c r="L15" s="242" t="n"/>
+      <c r="M15" s="245" t="n"/>
+      <c r="N15" s="245" t="n"/>
+      <c r="O15" s="70" t="n"/>
+      <c r="P15" s="70" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="180" t="inlineStr">
-        <is>
-          <t>COBRANZA RECUPERADA</t>
-        </is>
-      </c>
-      <c r="B16" s="181" t="n">
-        <v>115277</v>
-      </c>
-      <c r="C16" s="48" t="n"/>
-      <c r="D16" s="182" t="inlineStr">
-        <is>
-          <t>7.2%</t>
-        </is>
-      </c>
-      <c r="E16" s="48" t="n"/>
-      <c r="F16" s="201" t="inlineStr">
-        <is>
-          <t>▲ 2.3% vs mes anterior</t>
-        </is>
-      </c>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="48" t="n"/>
-      <c r="I16" s="48" t="n"/>
-      <c r="J16" s="48" t="n"/>
-      <c r="K16" s="48" t="n"/>
-      <c r="L16" s="48" t="n"/>
-      <c r="M16" s="53" t="n"/>
-      <c r="N16" s="53" t="n"/>
+      <c r="A16" s="124" t="n"/>
+      <c r="B16" s="125" t="n"/>
+      <c r="C16" s="242" t="n"/>
+      <c r="D16" s="246" t="n"/>
+      <c r="E16" s="242" t="n"/>
+      <c r="F16" s="247" t="n"/>
+      <c r="G16" s="242" t="n"/>
+      <c r="H16" s="242" t="n"/>
+      <c r="I16" s="242" t="n"/>
+      <c r="J16" s="242" t="n"/>
+      <c r="K16" s="242" t="n"/>
+      <c r="L16" s="242" t="n"/>
+      <c r="M16" s="245" t="n"/>
+      <c r="N16" s="245" t="n"/>
+      <c r="O16" s="70" t="n"/>
+      <c r="P16" s="70" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="184" t="inlineStr">
-        <is>
-          <t>COBRANZA EFECTIVA</t>
-        </is>
-      </c>
-      <c r="B17" s="185" t="n">
-        <v>1228968</v>
-      </c>
-      <c r="C17" s="48" t="n"/>
-      <c r="D17" s="186" t="inlineStr">
-        <is>
-          <t>76.7%</t>
-        </is>
-      </c>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="187" t="inlineStr">
-        <is>
-          <t>▲ 8.5% vs mes anterior</t>
-        </is>
-      </c>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="62" t="n"/>
-      <c r="I17" s="48" t="n"/>
-      <c r="J17" s="48" t="n"/>
-      <c r="K17" s="48" t="n"/>
-      <c r="L17" s="48" t="n"/>
-      <c r="M17" s="53" t="n"/>
-      <c r="N17" s="53" t="n"/>
+      <c r="A17" s="124" t="n"/>
+      <c r="B17" s="125" t="n"/>
+      <c r="C17" s="242" t="n"/>
+      <c r="D17" s="248" t="n"/>
+      <c r="E17" s="242" t="n"/>
+      <c r="F17" s="249" t="n"/>
+      <c r="G17" s="242" t="n"/>
+      <c r="H17" s="250" t="n"/>
+      <c r="I17" s="242" t="n"/>
+      <c r="J17" s="242" t="n"/>
+      <c r="K17" s="242" t="n"/>
+      <c r="L17" s="242" t="n"/>
+      <c r="M17" s="245" t="n"/>
+      <c r="N17" s="245" t="n"/>
+      <c r="O17" s="70" t="n"/>
+      <c r="P17" s="70" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="188" t="inlineStr">
-        <is>
-          <t>CANCELACIONES</t>
-        </is>
-      </c>
-      <c r="B18" s="189" t="n">
-        <v>127110</v>
-      </c>
-      <c r="C18" s="48" t="n"/>
-      <c r="D18" s="190" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="E18" s="48" t="n"/>
-      <c r="F18" s="191" t="inlineStr">
-        <is>
-          <t>▼ 1.1% vs mes anterior</t>
-        </is>
-      </c>
-      <c r="G18" s="48" t="n"/>
-      <c r="H18" s="48" t="n"/>
-      <c r="I18" s="48" t="n"/>
-      <c r="J18" s="62" t="n"/>
-      <c r="K18" s="48" t="n"/>
-      <c r="L18" s="48" t="n"/>
-      <c r="M18" s="53" t="n"/>
-      <c r="N18" s="53" t="n"/>
+      <c r="A18" s="124" t="n"/>
+      <c r="B18" s="125" t="n"/>
+      <c r="C18" s="242" t="n"/>
+      <c r="D18" s="251" t="n"/>
+      <c r="E18" s="242" t="n"/>
+      <c r="F18" s="252" t="n"/>
+      <c r="G18" s="242" t="n"/>
+      <c r="H18" s="242" t="n"/>
+      <c r="I18" s="242" t="n"/>
+      <c r="J18" s="250" t="n"/>
+      <c r="K18" s="242" t="n"/>
+      <c r="L18" s="242" t="n"/>
+      <c r="M18" s="245" t="n"/>
+      <c r="N18" s="245" t="n"/>
+      <c r="O18" s="70" t="n"/>
+      <c r="P18" s="70" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="192" t="inlineStr">
-        <is>
-          <t>COBRANZA VENCIDA</t>
-        </is>
-      </c>
-      <c r="B19" s="193" t="n">
-        <v>166220</v>
-      </c>
-      <c r="C19" s="48" t="n"/>
-      <c r="D19" s="194" t="inlineStr">
-        <is>
-          <t>10.4%</t>
-        </is>
-      </c>
-      <c r="E19" s="48" t="n"/>
-      <c r="F19" s="195" t="inlineStr">
-        <is>
-          <t>▼ vs mes anterior</t>
-        </is>
-      </c>
+      <c r="A19" s="124" t="n"/>
+      <c r="B19" s="125" t="n"/>
+      <c r="C19" s="242" t="n"/>
+      <c r="D19" s="253" t="n"/>
+      <c r="E19" s="242" t="n"/>
+      <c r="F19" s="254" t="n"/>
       <c r="G19" s="45" t="n"/>
       <c r="H19" s="46" t="n"/>
-      <c r="I19" s="48" t="n"/>
-      <c r="J19" s="48" t="n"/>
-      <c r="K19" s="48" t="n"/>
-      <c r="L19" s="62" t="n"/>
-      <c r="M19" s="53" t="n"/>
-      <c r="N19" s="53" t="n"/>
+      <c r="I19" s="242" t="n"/>
+      <c r="J19" s="242" t="n"/>
+      <c r="K19" s="242" t="n"/>
+      <c r="L19" s="250" t="n"/>
+      <c r="M19" s="245" t="n"/>
+      <c r="N19" s="245" t="n"/>
+      <c r="O19" s="70" t="n"/>
+      <c r="P19" s="70" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="196" t="inlineStr">
-        <is>
-          <t>TOTAL ACUMULADO</t>
-        </is>
-      </c>
-      <c r="B20" s="197" t="n">
-        <v>3046219</v>
-      </c>
-      <c r="C20" s="130" t="n"/>
-      <c r="D20" s="198" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E20" s="130" t="n"/>
-      <c r="F20" s="199" t="inlineStr">
-        <is>
-          <t>Suma de todos los conceptos</t>
-        </is>
-      </c>
-      <c r="G20" s="130" t="n"/>
-      <c r="H20" s="130" t="n"/>
-      <c r="I20" s="130" t="n"/>
-      <c r="J20" s="130" t="n"/>
-      <c r="K20" s="130" t="n"/>
-      <c r="L20" s="130" t="n"/>
-      <c r="M20" s="130" t="n"/>
-      <c r="N20" s="130" t="n"/>
+      <c r="A20" s="255" t="n"/>
+      <c r="B20" s="256" t="n"/>
+      <c r="C20" s="257" t="n"/>
+      <c r="D20" s="258" t="n"/>
+      <c r="E20" s="257" t="n"/>
+      <c r="F20" s="259" t="n"/>
+      <c r="G20" s="257" t="n"/>
+      <c r="H20" s="257" t="n"/>
+      <c r="I20" s="257" t="n"/>
+      <c r="J20" s="257" t="n"/>
+      <c r="K20" s="257" t="n"/>
+      <c r="L20" s="257" t="n"/>
+      <c r="M20" s="257" t="n"/>
+      <c r="N20" s="257" t="n"/>
+      <c r="O20" s="70" t="n"/>
+      <c r="P20" s="70" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="84" t="inlineStr">
@@ -4324,7 +4306,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="261" t="n">
         <v>166220</v>
       </c>
     </row>
@@ -4524,8 +4506,8 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B40" s="32" t="n">
-        <v>1228968</v>
+      <c r="B40" s="262" t="n">
+        <v>1073301</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -4724,8 +4706,8 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
-        <v>115277</v>
+      <c r="B49" s="261" t="n">
+        <v>103509</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -4924,8 +4906,8 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B58" s="32" t="n">
-        <v>1408644</v>
+      <c r="B58" s="262" t="n">
+        <v>1259266</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -5124,8 +5106,8 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B67" s="29" t="n">
-        <v>8618</v>
+      <c r="B67" s="261" t="n">
+        <v>4788</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -5314,8 +5296,8 @@
           <t>Proyeccion FEBRERO</t>
         </is>
       </c>
-      <c r="B76" s="33" t="n">
-        <v>1158184</v>
+      <c r="B76" s="263" t="n">
+        <v>1053199</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1"/>
@@ -18938,7 +18920,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="260">
+  <mergeCells count="258">
     <mergeCell ref="A362:N362"/>
     <mergeCell ref="A913:N913"/>
     <mergeCell ref="B231:D231"/>
@@ -19002,7 +18984,6 @@
     <mergeCell ref="B816:F816"/>
     <mergeCell ref="A705:N705"/>
     <mergeCell ref="A770:N770"/>
-    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A155:N155"/>
     <mergeCell ref="A245:B245"/>
     <mergeCell ref="A308:N308"/>
@@ -19188,7 +19169,6 @@
     <mergeCell ref="A420:B420"/>
     <mergeCell ref="A895:N895"/>
     <mergeCell ref="A140:N140"/>
-    <mergeCell ref="F19:H19"/>
     <mergeCell ref="B528:D528"/>
     <mergeCell ref="A622:N622"/>
     <mergeCell ref="A853:N853"/>

--- a/workspaces/cobranza/estadisticas/PLANTILLA_ESTADISTICA_JUNTA_MENSUAL_2026_ENERO_VFINAL.xlsx
+++ b/workspaces/cobranza/estadisticas/PLANTILLA_ESTADISTICA_JUNTA_MENSUAL_2026_ENERO_VFINAL.xlsx
@@ -2419,21 +2419,21 @@
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="221" t="inlineStr">
         <is>
-          <t>$1,259,266</t>
+          <t>$1,408,644</t>
         </is>
       </c>
       <c r="B8" s="163" t="n"/>
       <c r="C8" s="164" t="n"/>
       <c r="D8" s="222" t="inlineStr">
         <is>
-          <t>$103,509</t>
+          <t>$115,277</t>
         </is>
       </c>
       <c r="E8" s="171" t="n"/>
       <c r="F8" s="172" t="n"/>
       <c r="G8" s="223" t="inlineStr">
         <is>
-          <t>$1,073,301</t>
+          <t>$1,228,968</t>
         </is>
       </c>
       <c r="H8" s="169" t="n"/>
@@ -2451,7 +2451,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="225" t="inlineStr">
         <is>
-          <t>85.2% del total</t>
+          <t>87.2% del total</t>
         </is>
       </c>
       <c r="B9" s="45" t="n"/>
@@ -2465,14 +2465,14 @@
       <c r="F9" s="46" t="n"/>
       <c r="G9" s="227" t="inlineStr">
         <is>
-          <t>85.2% del total</t>
+          <t>87.2% del total</t>
         </is>
       </c>
       <c r="H9" s="45" t="n"/>
       <c r="I9" s="46" t="n"/>
       <c r="J9" s="228" t="inlineStr">
         <is>
-          <t>10.1% del total</t>
+          <t>9.0% del total</t>
         </is>
       </c>
       <c r="K9" s="45" t="n"/>
@@ -2535,7 +2535,7 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="221" t="inlineStr">
         <is>
-          <t>$1,476,747</t>
+          <t>$1,608,391</t>
         </is>
       </c>
       <c r="B12" s="163" t="n"/>
@@ -2549,14 +2549,14 @@
       <c r="F12" s="168" t="n"/>
       <c r="G12" s="233" t="inlineStr">
         <is>
-          <t>$4,788</t>
+          <t>$8,618</t>
         </is>
       </c>
       <c r="H12" s="173" t="n"/>
       <c r="I12" s="174" t="n"/>
       <c r="J12" s="234" t="inlineStr">
         <is>
-          <t>$1,053,199</t>
+          <t>$1,158,184</t>
         </is>
       </c>
       <c r="K12" s="175" t="n"/>
@@ -2574,14 +2574,14 @@
       <c r="C13" s="46" t="n"/>
       <c r="D13" s="235" t="inlineStr">
         <is>
-          <t>13.2% del total</t>
+          <t>11.8% del total</t>
         </is>
       </c>
       <c r="E13" s="45" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="236" t="inlineStr">
         <is>
-          <t>0.4% del total</t>
+          <t>0.6% del total</t>
         </is>
       </c>
       <c r="H13" s="45" t="n"/>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B18" s="177" t="n">
-        <v>1259266</v>
+        <v>1408644</v>
       </c>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="178" t="inlineStr">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="B19" s="181" t="n">
-        <v>103509</v>
+        <v>115277</v>
       </c>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="182" t="inlineStr">
@@ -2747,12 +2747,12 @@
         </is>
       </c>
       <c r="B20" s="185" t="n">
-        <v>1073301</v>
+        <v>1228968</v>
       </c>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="186" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="E20" s="38" t="n"/>
@@ -2782,7 +2782,7 @@
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="190" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="E21" s="38" t="n"/>
@@ -2812,7 +2812,7 @@
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="194" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="E22" s="38" t="n"/>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B23" s="197" t="n">
-        <v>2729406</v>
+        <v>3046219</v>
       </c>
       <c r="C23" s="130" t="n"/>
       <c r="D23" s="198" t="inlineStr">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B11" s="260" t="n">
-        <v>1476747</v>
+        <v>1608391</v>
       </c>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="38" t="n"/>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="B40" s="262" t="n">
-        <v>1073301</v>
+        <v>1228968</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="B49" s="261" t="n">
-        <v>103509</v>
+        <v>115277</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="B58" s="262" t="n">
-        <v>1259266</v>
+        <v>1408644</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="B67" s="261" t="n">
-        <v>4788</v>
+        <v>8618</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="B76" s="263" t="n">
-        <v>1053199</v>
+        <v>1158184</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1"/>

--- a/workspaces/cobranza/estadisticas/PLANTILLA_ESTADISTICA_JUNTA_MENSUAL_2026_ENERO_VFINAL.xlsx
+++ b/workspaces/cobranza/estadisticas/PLANTILLA_ESTADISTICA_JUNTA_MENSUAL_2026_ENERO_VFINAL.xlsx
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C5" s="91" t="inlineStr">
         <is>
-          <t>ENERO 2026</t>
+          <t>FEBRERO 2026</t>
         </is>
       </c>
       <c r="D5" s="162" t="n"/>
@@ -2417,31 +2417,23 @@
       <c r="N7" s="38" t="n"/>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="221" t="inlineStr">
-        <is>
-          <t>$1,408,644</t>
-        </is>
+      <c r="A8" s="221" t="n">
+        <v>1251614</v>
       </c>
       <c r="B8" s="163" t="n"/>
       <c r="C8" s="164" t="n"/>
-      <c r="D8" s="222" t="inlineStr">
-        <is>
-          <t>$115,277</t>
-        </is>
+      <c r="D8" s="222" t="n">
+        <v>94027</v>
       </c>
       <c r="E8" s="171" t="n"/>
       <c r="F8" s="172" t="n"/>
-      <c r="G8" s="223" t="inlineStr">
-        <is>
-          <t>$1,228,968</t>
-        </is>
+      <c r="G8" s="223" t="n">
+        <v>1110578</v>
       </c>
       <c r="H8" s="169" t="n"/>
       <c r="I8" s="170" t="n"/>
-      <c r="J8" s="224" t="inlineStr">
-        <is>
-          <t>$127,110</t>
-        </is>
+      <c r="J8" s="224" t="n">
+        <v>174435</v>
       </c>
       <c r="K8" s="165" t="n"/>
       <c r="L8" s="166" t="n"/>
@@ -2451,28 +2443,28 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="225" t="inlineStr">
         <is>
-          <t>87.2% del total</t>
+          <t>121.8% del total</t>
         </is>
       </c>
       <c r="B9" s="45" t="n"/>
       <c r="C9" s="46" t="n"/>
       <c r="D9" s="226" t="inlineStr">
         <is>
-          <t>8.2% del total</t>
+          <t>7.5% del total</t>
         </is>
       </c>
       <c r="E9" s="45" t="n"/>
       <c r="F9" s="46" t="n"/>
       <c r="G9" s="227" t="inlineStr">
         <is>
-          <t>87.2% del total</t>
+          <t>88.7% del total</t>
         </is>
       </c>
       <c r="H9" s="45" t="n"/>
       <c r="I9" s="46" t="n"/>
       <c r="J9" s="228" t="inlineStr">
         <is>
-          <t>9.0% del total</t>
+          <t>13.9% del total</t>
         </is>
       </c>
       <c r="K9" s="45" t="n"/>
@@ -2533,31 +2525,23 @@
       <c r="N11" s="38" t="n"/>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="221" t="inlineStr">
-        <is>
-          <t>$1,608,391</t>
-        </is>
+      <c r="A12" s="221" t="n">
+        <v>1524936</v>
       </c>
       <c r="B12" s="163" t="n"/>
       <c r="C12" s="164" t="n"/>
-      <c r="D12" s="232" t="inlineStr">
-        <is>
-          <t>$166,220</t>
-        </is>
+      <c r="D12" s="232" t="n">
+        <v>251487.31</v>
       </c>
       <c r="E12" s="167" t="n"/>
       <c r="F12" s="168" t="n"/>
-      <c r="G12" s="233" t="inlineStr">
-        <is>
-          <t>$8,618</t>
-        </is>
+      <c r="G12" s="233" t="n">
+        <v>3276933</v>
       </c>
       <c r="H12" s="173" t="n"/>
       <c r="I12" s="174" t="n"/>
-      <c r="J12" s="234" t="inlineStr">
-        <is>
-          <t>$1,158,184</t>
-        </is>
+      <c r="J12" s="234" t="n">
+        <v>1158184</v>
       </c>
       <c r="K12" s="175" t="n"/>
       <c r="L12" s="162" t="n"/>
@@ -2574,21 +2558,21 @@
       <c r="C13" s="46" t="n"/>
       <c r="D13" s="235" t="inlineStr">
         <is>
-          <t>11.8% del total</t>
+          <t>20.1% del total</t>
         </is>
       </c>
       <c r="E13" s="45" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="236" t="inlineStr">
         <is>
-          <t>0.6% del total</t>
+          <t>261.8% del total</t>
         </is>
       </c>
       <c r="H13" s="45" t="n"/>
       <c r="I13" s="46" t="n"/>
       <c r="J13" s="237" t="inlineStr">
         <is>
-          <t>Proyeccion FEB 2026</t>
+          <t>Proyeccion MAR 2026</t>
         </is>
       </c>
       <c r="K13" s="45" t="n"/>
@@ -2687,7 +2671,7 @@
         </is>
       </c>
       <c r="B18" s="177" t="n">
-        <v>1408644</v>
+        <v>1251614</v>
       </c>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="178" t="inlineStr">
@@ -2717,12 +2701,12 @@
         </is>
       </c>
       <c r="B19" s="181" t="n">
-        <v>115277</v>
+        <v>94027</v>
       </c>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="182" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E19" s="38" t="n"/>
@@ -2747,12 +2731,12 @@
         </is>
       </c>
       <c r="B20" s="185" t="n">
-        <v>1228968</v>
+        <v>1110578</v>
       </c>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="186" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="E20" s="38" t="n"/>
@@ -2777,12 +2761,12 @@
         </is>
       </c>
       <c r="B21" s="189" t="n">
-        <v>127110</v>
+        <v>174435</v>
       </c>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="190" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="E21" s="38" t="n"/>
@@ -2807,12 +2791,12 @@
         </is>
       </c>
       <c r="B22" s="193" t="n">
-        <v>166220</v>
+        <v>251487.31</v>
       </c>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="194" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="E22" s="38" t="n"/>
@@ -2837,7 +2821,7 @@
         </is>
       </c>
       <c r="B23" s="197" t="n">
-        <v>3046219</v>
+        <v>2882141.31</v>
       </c>
       <c r="C23" s="130" t="n"/>
       <c r="D23" s="198" t="inlineStr">
@@ -2994,11 +2978,11 @@
       </c>
       <c r="J27" s="148" t="inlineStr">
         <is>
-          <t>V39</t>
+          <t>V39 JOSE</t>
         </is>
       </c>
       <c r="K27" s="149" t="n">
-        <v>32232</v>
+        <v>70796.5</v>
       </c>
       <c r="M27" s="150" t="inlineStr">
         <is>
@@ -3048,11 +3032,11 @@
       </c>
       <c r="J28" s="154" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="K28" s="155" t="n">
-        <v>24988</v>
+        <v>40169</v>
       </c>
       <c r="M28" s="153" t="inlineStr">
         <is>
@@ -3097,16 +3081,16 @@
       </c>
       <c r="I29" s="147" t="inlineStr">
         <is>
-          <t>3o</t>
+          <t>3er</t>
         </is>
       </c>
       <c r="J29" s="148" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="K29" s="149" t="n">
-        <v>23648</v>
+        <v>35046</v>
       </c>
       <c r="M29" s="150" t="inlineStr">
         <is>
@@ -3156,11 +3140,11 @@
       </c>
       <c r="J30" s="154" t="inlineStr">
         <is>
-          <t>DEPTO</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="K30" s="155" t="n">
-        <v>19599</v>
+        <v>34647</v>
       </c>
       <c r="M30" s="153" t="inlineStr">
         <is>
@@ -3210,11 +3194,11 @@
       </c>
       <c r="J31" s="148" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>DEPOSITO</t>
         </is>
       </c>
       <c r="K31" s="149" t="n">
-        <v>16160</v>
+        <v>24103.81</v>
       </c>
       <c r="M31" s="150" t="inlineStr">
         <is>
@@ -3310,6 +3294,25 @@
       </c>
       <c r="E39" s="157" t="n">
         <v>1408644</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FEB 2026</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1110578</v>
+      </c>
+      <c r="C40" t="n">
+        <v>251487.31</v>
+      </c>
+      <c r="D40" t="n">
+        <v>94027</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1251614</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
@@ -5768,7 +5771,9 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B105" s="11" t="n"/>
+      <c r="B105" s="11" t="n">
+        <v>251487.31</v>
+      </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="12" t="inlineStr">
@@ -5796,8 +5801,14 @@
         </is>
       </c>
       <c r="B107" s="15" t="n"/>
-      <c r="C107" s="15" t="n"/>
-      <c r="D107" s="15" t="n"/>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>V39 JOSE</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="n">
+        <v>70796.5</v>
+      </c>
       <c r="E107" s="15" t="n"/>
       <c r="F107" s="15" t="n"/>
       <c r="G107" s="15" t="n"/>
@@ -5806,8 +5817,12 @@
       <c r="J107" s="15" t="n"/>
       <c r="K107" s="15" t="n"/>
       <c r="L107" s="15" t="n"/>
-      <c r="M107" s="15" t="n"/>
-      <c r="N107" s="15" t="n"/>
+      <c r="M107" s="15" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="N107" s="15" t="n">
+        <v>0.2815</v>
+      </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="14" t="inlineStr">
@@ -5818,16 +5833,26 @@
       <c r="B108" s="15" t="n"/>
       <c r="C108" s="15" t="n"/>
       <c r="D108" s="15" t="n"/>
-      <c r="E108" s="15" t="n"/>
-      <c r="F108" s="15" t="n"/>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>40169</v>
+      </c>
       <c r="G108" s="15" t="n"/>
       <c r="H108" s="15" t="n"/>
       <c r="I108" s="15" t="n"/>
       <c r="J108" s="15" t="n"/>
       <c r="K108" s="15" t="n"/>
       <c r="L108" s="15" t="n"/>
-      <c r="M108" s="15" t="n"/>
-      <c r="N108" s="15" t="n"/>
+      <c r="M108" s="15" t="n">
+        <v>0.1597</v>
+      </c>
+      <c r="N108" s="15" t="n">
+        <v>0.4412</v>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="14" t="inlineStr">
@@ -5840,14 +5865,24 @@
       <c r="D109" s="15" t="n"/>
       <c r="E109" s="15" t="n"/>
       <c r="F109" s="15" t="n"/>
-      <c r="G109" s="15" t="n"/>
-      <c r="H109" s="15" t="n"/>
+      <c r="G109" s="15" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>35046</v>
+      </c>
       <c r="I109" s="15" t="n"/>
       <c r="J109" s="15" t="n"/>
       <c r="K109" s="15" t="n"/>
       <c r="L109" s="15" t="n"/>
-      <c r="M109" s="15" t="n"/>
-      <c r="N109" s="15" t="n"/>
+      <c r="M109" s="15" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="N109" s="15" t="n">
+        <v>0.5806</v>
+      </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="14" t="inlineStr">
@@ -5862,12 +5897,22 @@
       <c r="F110" s="15" t="n"/>
       <c r="G110" s="15" t="n"/>
       <c r="H110" s="15" t="n"/>
-      <c r="I110" s="15" t="n"/>
-      <c r="J110" s="15" t="n"/>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J110" s="15" t="n">
+        <v>34647</v>
+      </c>
       <c r="K110" s="15" t="n"/>
       <c r="L110" s="15" t="n"/>
-      <c r="M110" s="15" t="n"/>
-      <c r="N110" s="15" t="n"/>
+      <c r="M110" s="15" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="N110" s="15" t="n">
+        <v>0.7184</v>
+      </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="14" t="inlineStr">
@@ -5884,10 +5929,20 @@
       <c r="H111" s="15" t="n"/>
       <c r="I111" s="15" t="n"/>
       <c r="J111" s="15" t="n"/>
-      <c r="K111" s="15" t="n"/>
-      <c r="L111" s="15" t="n"/>
-      <c r="M111" s="15" t="n"/>
-      <c r="N111" s="15" t="n"/>
+      <c r="K111" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="L111" s="15" t="n">
+        <v>24103.81</v>
+      </c>
+      <c r="M111" s="15" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="N111" s="15" t="n">
+        <v>0.8142</v>
+      </c>
     </row>
     <row r="112" ht="6" customHeight="1"/>
     <row r="113">
